--- a/data/memories/memory_01/locales/es/documents/director/Historical_Index.xlsx
+++ b/data/memories/memory_01/locales/es/documents/director/Historical_Index.xlsx
@@ -433,7 +433,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Historical Index</t>
+          <t>Índice histórico</t>
         </is>
       </c>
     </row>
@@ -445,7 +445,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Interno</t>
         </is>
       </c>
     </row>
@@ -469,99 +469,99 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Administration</t>
+          <t>Administración</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Historical Document Index</t>
+          <t>Índice de documentos históricos</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Categoría</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Location</t>
+          <t>Ubicación</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Estado</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Employee records</t>
+          <t>Registros de empleados</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Archive</t>
+          <t>Archivo</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Retained</t>
+          <t>Retenido</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Contracts</t>
+          <t>Contratos</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Archive</t>
+          <t>Archivo</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Retained</t>
+          <t>Retenido</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Organisation</t>
+          <t>Organización</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Archive</t>
+          <t>Archivo</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Multiple versions</t>
+          <t>Múltiples versiones</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Management records</t>
+          <t>Registros de gestión</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Director's Office</t>
+          <t>oficina del director</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Restricted</t>
+          <t>Restringido</t>
         </is>
       </c>
     </row>
